--- a/output/pdf_financials_xlsx/ERE.UN.xlsx
+++ b/output/pdf_financials_xlsx/ERE.UN.xlsx
@@ -2053,16 +2053,16 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.000477</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.00129</v>
       </c>
     </row>
     <row r="41">
@@ -2086,16 +2086,16 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1.968</v>
+        <v>2.435</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2.434</v>
+        <v>2.499</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>2.434</v>
+        <v>2.434477</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.002935</v>
+        <v>0.004225</v>
       </c>
     </row>
     <row r="42">
@@ -2851,13 +2851,11 @@
       <c r="D64" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="3" t="n">
+        <v>2.619</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -2956,16 +2954,16 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>3.247</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>2.697</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.001242</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.002813</v>
       </c>
     </row>
     <row r="68">
@@ -2983,10 +2981,8 @@
       <c r="D68" s="3" t="n">
         <v>1.195727</v>
       </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E68" s="3" t="n">
+        <v>2.619</v>
       </c>
       <c r="F68" s="3" t="n">
         <v>7.424</v>
@@ -5264,13 +5260,13 @@
         </is>
       </c>
       <c r="G132" s="3" t="n">
-        <v>-0.01</v>
+        <v>58.826</v>
       </c>
       <c r="H132" s="3" t="n">
-        <v>0.007</v>
+        <v>55.22</v>
       </c>
       <c r="I132" s="3" t="n">
-        <v>-6e-06</v>
+        <v>0.054874</v>
       </c>
     </row>
     <row r="133">
@@ -5301,13 +5297,13 @@
         </is>
       </c>
       <c r="G133" s="3" t="n">
-        <v>10.338</v>
+        <v>69.17400000000001</v>
       </c>
       <c r="H133" s="3" t="n">
-        <v>10.896</v>
+        <v>66.10899999999999</v>
       </c>
       <c r="I133" s="3" t="n">
-        <v>0.006887</v>
+        <v>0.061767</v>
       </c>
     </row>
     <row r="134">
@@ -5378,20 +5374,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G135" s="3" t="n">
+        <v>58.836</v>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>55.213</v>
+      </c>
+      <c r="I135" s="3" t="n">
+        <v>0.05488</v>
       </c>
     </row>
   </sheetData>
@@ -23566,7 +23556,11 @@
           <t>Deferred income tax expense 1,677</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -23900,7 +23894,11 @@
           <t>Net Cash Generated from Operating Activities 15,241</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr"/>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E329" t="inlineStr">
         <is>
           <t>-</t>
@@ -24068,7 +24066,11 @@
           <t>Net Cash Generated from Investing Activities 468,720</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -25532,7 +25534,11 @@
           <t>Deferred income tax expense (recovery) 21 15,268</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -25814,7 +25820,11 @@
           <t>Net Cash Generated from Operating Activities 54,880</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E363" t="inlineStr">
         <is>
           <t>-</t>
@@ -27950,7 +27960,11 @@
           <t>Net Cash Generated from Operating Activities 55,213</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
